--- a/04_Figures/F04_association/modules/T2/limma/c_data/results.xlsx
+++ b/04_Figures/F04_association/modules/T2/limma/c_data/results.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t xml:space="preserve">outcome</t>
   </si>
@@ -70,12 +70,6 @@
   </si>
   <si>
     <t xml:space="preserve">ME_red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_salmon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_tan</t>
   </si>
   <si>
     <t xml:space="preserve">ME_turquoise</t>
@@ -492,16 +486,16 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.000410666246724345</v>
+        <v>0.000317992420920528</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0929394740733259</v>
+        <v>0.0803021040758075</v>
       </c>
       <c r="F2" t="n">
-        <v>0.926061730516495</v>
+        <v>0.936109258364661</v>
       </c>
       <c r="G2" t="n">
-        <v>0.999097589191704</v>
+        <v>0.991331650853256</v>
       </c>
     </row>
     <row r="3">
@@ -515,16 +509,16 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00307118796967363</v>
+        <v>0.00148087801174252</v>
       </c>
       <c r="E3" t="n">
-        <v>0.695052483515617</v>
+        <v>0.373963693468789</v>
       </c>
       <c r="F3" t="n">
-        <v>0.487976944702737</v>
+        <v>0.708985219656262</v>
       </c>
       <c r="G3" t="n">
-        <v>0.999097589191704</v>
+        <v>0.97485467702736</v>
       </c>
     </row>
     <row r="4">
@@ -538,16 +532,16 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.00125861750219716</v>
+        <v>0.00489566898620208</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.284842617689506</v>
+        <v>1.23629525292665</v>
       </c>
       <c r="F4" t="n">
-        <v>0.776113471332726</v>
+        <v>0.218375615228857</v>
       </c>
       <c r="G4" t="n">
-        <v>0.999097589191704</v>
+        <v>0.97485467702736</v>
       </c>
     </row>
     <row r="5">
@@ -561,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0015727117811712</v>
+        <v>-0.00188504296308598</v>
       </c>
       <c r="E5" t="n">
-        <v>0.355926514479501</v>
+        <v>-0.476026805201529</v>
       </c>
       <c r="F5" t="n">
-        <v>0.722339502634703</v>
+        <v>0.634781738773379</v>
       </c>
       <c r="G5" t="n">
-        <v>0.999097589191704</v>
+        <v>0.97485467702736</v>
       </c>
     </row>
     <row r="6">
@@ -584,16 +578,16 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00000500490181898343</v>
+        <v>-0.0000430976968291628</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0011326787788264</v>
+        <v>-0.0108833906361182</v>
       </c>
       <c r="F6" t="n">
-        <v>0.999097589191704</v>
+        <v>0.991331650853256</v>
       </c>
       <c r="G6" t="n">
-        <v>0.999097589191704</v>
+        <v>0.991331650853256</v>
       </c>
     </row>
     <row r="7">
@@ -607,16 +601,16 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00206205915241097</v>
+        <v>0.000188164987104191</v>
       </c>
       <c r="E7" t="n">
-        <v>0.466672619582987</v>
+        <v>0.0475169953237344</v>
       </c>
       <c r="F7" t="n">
-        <v>0.64133515261202</v>
+        <v>0.962167483032523</v>
       </c>
       <c r="G7" t="n">
-        <v>0.999097589191704</v>
+        <v>0.991331650853256</v>
       </c>
     </row>
     <row r="8">
@@ -630,16 +624,16 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00494566575228897</v>
+        <v>0.00203979642127084</v>
       </c>
       <c r="E8" t="n">
-        <v>1.11927283439179</v>
+        <v>0.515106441971731</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2646120430398</v>
+        <v>0.607273976999737</v>
       </c>
       <c r="G8" t="n">
-        <v>0.999097589191704</v>
+        <v>0.97485467702736</v>
       </c>
     </row>
     <row r="9">
@@ -653,16 +647,16 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.000261067424282661</v>
+        <v>0.00500378453119508</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0590831832517146</v>
+        <v>1.26359749403387</v>
       </c>
       <c r="F9" t="n">
-        <v>0.952955658324711</v>
+        <v>0.208430638735793</v>
       </c>
       <c r="G9" t="n">
-        <v>0.999097589191704</v>
+        <v>0.97485467702736</v>
       </c>
     </row>
     <row r="10">
@@ -676,16 +670,16 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.00134028334768443</v>
+        <v>0.00334961623232757</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.303324732520909</v>
+        <v>0.845873088810523</v>
       </c>
       <c r="F10" t="n">
-        <v>0.762015478107634</v>
+        <v>0.399036736991259</v>
       </c>
       <c r="G10" t="n">
-        <v>0.999097589191704</v>
+        <v>0.97485467702736</v>
       </c>
     </row>
     <row r="11">
@@ -699,16 +693,16 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.00233626320644739</v>
+        <v>-0.00401085960662853</v>
       </c>
       <c r="E11" t="n">
-        <v>0.528728804560919</v>
+        <v>-1.01285579270278</v>
       </c>
       <c r="F11" t="n">
-        <v>0.597687290029282</v>
+        <v>0.31283973624621</v>
       </c>
       <c r="G11" t="n">
-        <v>0.999097589191704</v>
+        <v>0.97485467702736</v>
       </c>
     </row>
     <row r="12">
@@ -722,62 +716,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.00275537427518954</v>
+        <v>-0.0022299398348296</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.623579459120194</v>
+        <v>-0.563123046080484</v>
       </c>
       <c r="F12" t="n">
-        <v>0.533744524829869</v>
+        <v>0.574232975850615</v>
       </c>
       <c r="G12" t="n">
-        <v>0.999097589191704</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.00405650317474784</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.918042996338348</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.359904688227667</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.999097589191704</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.00378343864007997</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.856244700416686</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.393074863044824</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.999097589191704</v>
+        <v>0.97485467702736</v>
       </c>
     </row>
   </sheetData>
@@ -816,7 +764,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -825,21 +773,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0000320017650478153</v>
+        <v>0.0000176134630180144</v>
       </c>
       <c r="E2" t="n">
-        <v>1.26193336733876</v>
+        <v>0.767749603498167</v>
       </c>
       <c r="F2" t="n">
-        <v>0.208711590152746</v>
+        <v>0.443901838868076</v>
       </c>
       <c r="G2" t="n">
-        <v>0.530448093598113</v>
+        <v>0.610365028443604</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -848,21 +796,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0000246225407425614</v>
+        <v>-0.000025858170896934</v>
       </c>
       <c r="E3" t="n">
-        <v>0.970946624514936</v>
+        <v>-1.1271264732554</v>
       </c>
       <c r="F3" t="n">
-        <v>0.332962442925323</v>
+        <v>0.26157676607818</v>
       </c>
       <c r="G3" t="n">
-        <v>0.530448093598113</v>
+        <v>0.446014113440358</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -871,21 +819,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00000861769091875154</v>
+        <v>0.0000298834867067425</v>
       </c>
       <c r="E4" t="n">
-        <v>0.339823497345726</v>
+        <v>1.30258513313248</v>
       </c>
       <c r="F4" t="n">
-        <v>0.734411418233841</v>
+        <v>0.19481030237927</v>
       </c>
       <c r="G4" t="n">
-        <v>0.795612369753328</v>
+        <v>0.446014113440358</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -894,21 +842,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0000210335128424581</v>
+        <v>-0.00000851960005087293</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.829419616342638</v>
+        <v>-0.37135908789378</v>
       </c>
       <c r="F5" t="n">
-        <v>0.408036995075471</v>
+        <v>0.710919724719146</v>
       </c>
       <c r="G5" t="n">
-        <v>0.530448093598113</v>
+        <v>0.868901885767845</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -917,21 +865,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0000274271160039865</v>
+        <v>0.0000272340532322702</v>
       </c>
       <c r="E6" t="n">
-        <v>1.08154012141478</v>
+        <v>1.18709952434331</v>
       </c>
       <c r="F6" t="n">
-        <v>0.280997789067796</v>
+        <v>0.237156622815869</v>
       </c>
       <c r="G6" t="n">
-        <v>0.530448093598113</v>
+        <v>0.446014113440358</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -940,21 +888,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0000222606066946696</v>
+        <v>0.0000306229503998608</v>
       </c>
       <c r="E7" t="n">
-        <v>0.877807906008794</v>
+        <v>1.33481746340236</v>
       </c>
       <c r="F7" t="n">
-        <v>0.381294191278304</v>
+        <v>0.184057386542671</v>
       </c>
       <c r="G7" t="n">
-        <v>0.530448093598113</v>
+        <v>0.446014113440358</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -963,21 +911,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0000390734758065292</v>
+        <v>0.0000256561625278057</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5407938538543</v>
+        <v>1.11832117215459</v>
       </c>
       <c r="F8" t="n">
-        <v>0.12523729304987</v>
+        <v>0.265304998851386</v>
       </c>
       <c r="G8" t="n">
-        <v>0.530448093598113</v>
+        <v>0.446014113440358</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -986,21 +934,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0000240544926575749</v>
+        <v>0.0000246807199784385</v>
       </c>
       <c r="E9" t="n">
-        <v>0.948546646525404</v>
+        <v>1.07580280823343</v>
       </c>
       <c r="F9" t="n">
-        <v>0.34420564739667</v>
+        <v>0.28382716309841</v>
       </c>
       <c r="G9" t="n">
-        <v>0.530448093598113</v>
+        <v>0.446014113440358</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -1009,21 +957,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.00000942234066134044</v>
+        <v>0.00000215500887909498</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.371553445918134</v>
+        <v>0.0939342371666508</v>
       </c>
       <c r="F10" t="n">
-        <v>0.710690768420788</v>
+        <v>0.925292883433543</v>
       </c>
       <c r="G10" t="n">
-        <v>0.795612369753328</v>
+        <v>0.925292883433543</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -1032,21 +980,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0000283103985728775</v>
+        <v>-0.000032030745492246</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.11637081730943</v>
+        <v>-1.39618155306945</v>
       </c>
       <c r="F11" t="n">
-        <v>0.265848175812627</v>
+        <v>0.164823450055845</v>
       </c>
       <c r="G11" t="n">
-        <v>0.530448093598113</v>
+        <v>0.446014113440358</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -1055,62 +1003,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0000421971747356275</v>
+        <v>0.00000224252297412505</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.66397143178663</v>
+        <v>0.0977488709891492</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0979712608459155</v>
+        <v>0.922268583278905</v>
       </c>
       <c r="G12" t="n">
-        <v>0.530448093598113</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.0000316676022355516</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-1.24875624406793</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.213481277724744</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.530448093598113</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.000000375690302260072</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.0148146868617778</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.98819749714618</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.98819749714618</v>
+        <v>0.925292883433543</v>
       </c>
     </row>
   </sheetData>
@@ -1149,7 +1051,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -1158,21 +1060,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0000188560688458646</v>
+        <v>0.0000191588791620754</v>
       </c>
       <c r="E2" t="n">
-        <v>0.68952849524956</v>
+        <v>0.771529888016685</v>
       </c>
       <c r="F2" t="n">
-        <v>0.491436427049768</v>
+        <v>0.441665966115047</v>
       </c>
       <c r="G2" t="n">
-        <v>0.638867355164698</v>
+        <v>0.645369074867254</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -1181,21 +1083,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0000249713720573318</v>
+        <v>-0.0000313133774352542</v>
       </c>
       <c r="E3" t="n">
-        <v>0.913152828394828</v>
+        <v>-1.26099269073467</v>
       </c>
       <c r="F3" t="n">
-        <v>0.362463027124967</v>
+        <v>0.209364888682541</v>
       </c>
       <c r="G3" t="n">
-        <v>0.578178543542371</v>
+        <v>0.603154037417241</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -1204,21 +1106,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0000100411713472569</v>
+        <v>0.0000295078619753509</v>
       </c>
       <c r="E4" t="n">
-        <v>0.367185431184693</v>
+        <v>1.18828441125718</v>
       </c>
       <c r="F4" t="n">
-        <v>0.713940084158182</v>
+        <v>0.236691126159566</v>
       </c>
       <c r="G4" t="n">
-        <v>0.773435091171364</v>
+        <v>0.603154037417241</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -1227,21 +1129,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0000260098904521757</v>
+        <v>-0.0000100172528270185</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.951129356373128</v>
+        <v>-0.403395725109172</v>
       </c>
       <c r="F5" t="n">
-        <v>0.342896979042707</v>
+        <v>0.687259663761266</v>
       </c>
       <c r="G5" t="n">
-        <v>0.578178543542371</v>
+        <v>0.839984033485992</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -1250,21 +1152,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0000230599388309732</v>
+        <v>0.00002353149793292</v>
       </c>
       <c r="E6" t="n">
-        <v>0.84325556151939</v>
+        <v>0.947615662245449</v>
       </c>
       <c r="F6" t="n">
-        <v>0.400277453221642</v>
+        <v>0.344923755660305</v>
       </c>
       <c r="G6" t="n">
-        <v>0.578178543542371</v>
+        <v>0.63236021871056</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -1273,21 +1175,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0000233959161187525</v>
+        <v>0.0000180146982163603</v>
       </c>
       <c r="E7" t="n">
-        <v>0.855541574875311</v>
+        <v>0.7254536123927</v>
       </c>
       <c r="F7" t="n">
-        <v>0.393462712476733</v>
+        <v>0.469359327176185</v>
       </c>
       <c r="G7" t="n">
-        <v>0.578178543542371</v>
+        <v>0.645369074867254</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -1296,21 +1198,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0000440920168837411</v>
+        <v>0.0000302499495547361</v>
       </c>
       <c r="E8" t="n">
-        <v>1.61235633486944</v>
+        <v>1.21816834873485</v>
       </c>
       <c r="F8" t="n">
-        <v>0.108750298371741</v>
+        <v>0.225166052123891</v>
       </c>
       <c r="G8" t="n">
-        <v>0.578178543542371</v>
+        <v>0.603154037417241</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -1319,21 +1221,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0000285243004696652</v>
+        <v>0.0000272595522957856</v>
       </c>
       <c r="E9" t="n">
-        <v>1.04307627118195</v>
+        <v>1.09774476639448</v>
       </c>
       <c r="F9" t="n">
-        <v>0.298402752589552</v>
+        <v>0.274160926098746</v>
       </c>
       <c r="G9" t="n">
-        <v>0.578178543542371</v>
+        <v>0.603154037417241</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -1342,21 +1244,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0000113648467232977</v>
+        <v>0.00000424657266206433</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.415589576168523</v>
+        <v>0.17100988542705</v>
       </c>
       <c r="F10" t="n">
-        <v>0.67823755293975</v>
+        <v>0.864457729279146</v>
       </c>
       <c r="G10" t="n">
-        <v>0.773435091171364</v>
+        <v>0.932396206696524</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -1365,21 +1267,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.000040876038360548</v>
+        <v>-0.0000275900381641809</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.49475447151294</v>
+        <v>-1.11105346378106</v>
       </c>
       <c r="F11" t="n">
-        <v>0.136843412869925</v>
+        <v>0.268409943550317</v>
       </c>
       <c r="G11" t="n">
-        <v>0.578178543542371</v>
+        <v>0.603154037417241</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -1388,62 +1290,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0000409149606215944</v>
+        <v>0.00000211024901136606</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.49617778027949</v>
+        <v>0.0849799286092584</v>
       </c>
       <c r="F12" t="n">
-        <v>0.136472480233274</v>
+        <v>0.932396206696524</v>
       </c>
       <c r="G12" t="n">
-        <v>0.578178543542371</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.0000271634106480546</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.993311268807056</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.321978362054485</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.578178543542371</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.0000010087500120065</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.0368879581182884</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.970617877296084</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.970617877296084</v>
+        <v>0.932396206696524</v>
       </c>
     </row>
   </sheetData>
@@ -1482,7 +1338,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -1491,21 +1347,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0345444536509103</v>
+        <v>-0.0230729182193341</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.85100596089742</v>
+        <v>-1.35376932818721</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0668393506863215</v>
+        <v>0.177945746241288</v>
       </c>
       <c r="G2" t="n">
-        <v>0.144818593153696</v>
+        <v>0.326233868109029</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -1514,21 +1370,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.00535529512917307</v>
+        <v>0.0557705718084619</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.295425804145658</v>
+        <v>3.27225575941635</v>
       </c>
       <c r="F3" t="n">
-        <v>0.768223037971032</v>
+        <v>0.0013376048203394</v>
       </c>
       <c r="G3" t="n">
-        <v>0.84113623408905</v>
+        <v>0.0147136530237334</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -1537,21 +1393,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0261500728190795</v>
+        <v>0.0066949424099134</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.45536167607175</v>
+        <v>0.392815837266992</v>
       </c>
       <c r="F4" t="n">
-        <v>0.148404338232967</v>
+        <v>0.69504044873199</v>
       </c>
       <c r="G4" t="n">
-        <v>0.275608056718368</v>
+        <v>0.764544493605189</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -1560,21 +1416,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0482579570851503</v>
+        <v>0.00335319968177346</v>
       </c>
       <c r="E5" t="n">
-        <v>2.73981635833066</v>
+        <v>0.196744028532471</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00716953725159897</v>
+        <v>0.844307198089892</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0466019921353933</v>
+        <v>0.844307198089892</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -1583,21 +1439,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0410373625682178</v>
+        <v>-0.0409920000141404</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.25183617208939</v>
+        <v>-2.40514493193548</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0263095631612858</v>
+        <v>0.0174448870030316</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0855060802741789</v>
+        <v>0.095946878516674</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -1606,21 +1462,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00376819167451363</v>
+        <v>-0.0348835570419693</v>
       </c>
       <c r="E7" t="n">
-        <v>0.200912647659166</v>
+        <v>-2.04674108114834</v>
       </c>
       <c r="F7" t="n">
-        <v>0.84113623408905</v>
+        <v>0.0425149603768276</v>
       </c>
       <c r="G7" t="n">
-        <v>0.84113623408905</v>
+        <v>0.155888188048368</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -1629,21 +1485,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0046073881359641</v>
+        <v>-0.0086145505035526</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.250545782365831</v>
+        <v>-0.505446001106912</v>
       </c>
       <c r="F8" t="n">
-        <v>0.802630574122214</v>
+        <v>0.614023789320106</v>
       </c>
       <c r="G8" t="n">
-        <v>0.84113623408905</v>
+        <v>0.764544493605189</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -1652,21 +1508,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0245660024104245</v>
+        <v>0.0122004576901145</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.36311916544454</v>
+        <v>0.715843798071572</v>
       </c>
       <c r="F9" t="n">
-        <v>0.175616166161646</v>
+        <v>0.475255090580394</v>
       </c>
       <c r="G9" t="n">
-        <v>0.285376270012675</v>
+        <v>0.746829428054905</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -1675,21 +1531,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.00883967309398138</v>
+        <v>0.0298613995918631</v>
       </c>
       <c r="E10" t="n">
-        <v>0.482824333192939</v>
+        <v>1.75207342564634</v>
       </c>
       <c r="F10" t="n">
-        <v>0.630175680005735</v>
+        <v>0.0819047525132845</v>
       </c>
       <c r="G10" t="n">
-        <v>0.84113623408905</v>
+        <v>0.225238069411532</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -1698,21 +1554,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0723979715730904</v>
+        <v>-0.00674685051384614</v>
       </c>
       <c r="E11" t="n">
-        <v>3.74662757335061</v>
+        <v>-0.395861468440322</v>
       </c>
       <c r="F11" t="n">
-        <v>0.00028667480706331</v>
+        <v>0.692797221448323</v>
       </c>
       <c r="G11" t="n">
-        <v>0.00372677249182303</v>
+        <v>0.764544493605189</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -1721,62 +1577,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.042543816857442</v>
+        <v>-0.0253944287951217</v>
       </c>
       <c r="E12" t="n">
-        <v>2.31809254435504</v>
+        <v>-1.48998052534432</v>
       </c>
       <c r="F12" t="n">
-        <v>0.022285119050374</v>
+        <v>0.138431706050523</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0855060802741789</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.00788587591278982</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.422276928698458</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.67364342272376</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.84113623408905</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.0358484991609269</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1.99385080711377</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.0486318122473812</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.126442711843191</v>
+        <v>0.30454975331115</v>
       </c>
     </row>
   </sheetData>
@@ -1815,7 +1625,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -1824,21 +1634,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.000783456118573346</v>
+        <v>0.00133471164445609</v>
       </c>
       <c r="E2" t="n">
-        <v>0.692366665993189</v>
+        <v>1.3067856554373</v>
       </c>
       <c r="F2" t="n">
-        <v>0.489657321535924</v>
+        <v>0.193383155991192</v>
       </c>
       <c r="G2" t="n">
-        <v>0.743628436679814</v>
+        <v>0.425442943180622</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -1847,21 +1657,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00176005405676157</v>
+        <v>-0.000822650596531335</v>
       </c>
       <c r="E3" t="n">
-        <v>1.55541928942599</v>
+        <v>-0.805438390718599</v>
       </c>
       <c r="F3" t="n">
-        <v>0.121716932203836</v>
+        <v>0.421903991717789</v>
       </c>
       <c r="G3" t="n">
-        <v>0.263720019774978</v>
+        <v>0.590941651314465</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -1870,21 +1680,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.000640669035483046</v>
+        <v>0.00150820253908589</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5661808920584</v>
+        <v>1.47664662382917</v>
       </c>
       <c r="F4" t="n">
-        <v>0.572021874369087</v>
+        <v>0.141969178329914</v>
       </c>
       <c r="G4" t="n">
-        <v>0.743628436679814</v>
+        <v>0.390415240407263</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -1893,21 +1703,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.000674967213275449</v>
+        <v>0.000439058158000494</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.596491351629525</v>
+        <v>0.429871804266442</v>
       </c>
       <c r="F5" t="n">
-        <v>0.55164519648031</v>
+        <v>0.667935967942824</v>
       </c>
       <c r="G5" t="n">
-        <v>0.743628436679814</v>
+        <v>0.734729564737106</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -1916,21 +1726,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00176349066338809</v>
+        <v>0.00194771239508479</v>
       </c>
       <c r="E6" t="n">
-        <v>1.55845633491702</v>
+        <v>1.90696067527863</v>
       </c>
       <c r="F6" t="n">
-        <v>0.120995793133333</v>
+        <v>0.0585311951636474</v>
       </c>
       <c r="G6" t="n">
-        <v>0.263720019774978</v>
+        <v>0.305307415826788</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -1939,21 +1749,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.000529934913379162</v>
+        <v>0.00080874363592692</v>
       </c>
       <c r="E7" t="n">
-        <v>0.468321403677149</v>
+        <v>0.791822403547086</v>
       </c>
       <c r="F7" t="n">
-        <v>0.640158215893892</v>
+        <v>0.42977574641052</v>
       </c>
       <c r="G7" t="n">
-        <v>0.75655061878369</v>
+        <v>0.590941651314465</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -1962,21 +1772,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00198595858880702</v>
+        <v>0.00178151608589266</v>
       </c>
       <c r="E8" t="n">
-        <v>1.75505876377189</v>
+        <v>1.74424166871193</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0810613088510768</v>
+        <v>0.0832656588618512</v>
       </c>
       <c r="G8" t="n">
-        <v>0.263720019774978</v>
+        <v>0.305307415826788</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -1985,21 +1795,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00178930305985671</v>
+        <v>0.00101034422976069</v>
       </c>
       <c r="E9" t="n">
-        <v>1.58126762257001</v>
+        <v>0.989204935754611</v>
       </c>
       <c r="F9" t="n">
-        <v>0.11568658488422</v>
+        <v>0.324233715178439</v>
       </c>
       <c r="G9" t="n">
-        <v>0.263720019774978</v>
+        <v>0.590941651314465</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -2008,21 +1818,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.000393397107102595</v>
+        <v>0.00000717133868206028</v>
       </c>
       <c r="E10" t="n">
-        <v>0.347658326993447</v>
+        <v>0.00702129374455107</v>
       </c>
       <c r="F10" t="n">
-        <v>0.728529408378181</v>
+        <v>0.994407649783212</v>
       </c>
       <c r="G10" t="n">
-        <v>0.789240192409696</v>
+        <v>0.994407649783212</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -2031,21 +1841,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.00244867736553228</v>
+        <v>-0.00200687601033749</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.16397899445067</v>
+        <v>-1.96488641830873</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0318698020569858</v>
+        <v>0.0513655627940702</v>
       </c>
       <c r="G11" t="n">
-        <v>0.263720019774978</v>
+        <v>0.305307415826788</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -2054,62 +1864,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.00113375938244125</v>
+        <v>0.000715556586122318</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.00194150642255</v>
+        <v>0.700585093628509</v>
       </c>
       <c r="F12" t="n">
-        <v>0.317804274127862</v>
+        <v>0.484700322286988</v>
       </c>
       <c r="G12" t="n">
-        <v>0.59020793766603</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.0019711051997409</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-1.74193232155948</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.0833396600463568</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.263720019774978</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.0000519013723804849</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.0458669979130212</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.963470411688077</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.963470411688077</v>
+        <v>0.59241150501743</v>
       </c>
     </row>
   </sheetData>
@@ -2148,7 +1912,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -2157,21 +1921,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.00434924038756749</v>
+        <v>-0.00377733809605316</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.76567823567819</v>
+        <v>-0.735491012586491</v>
       </c>
       <c r="F2" t="n">
-        <v>0.445024702605847</v>
+        <v>0.46334534713376</v>
       </c>
       <c r="G2" t="n">
-        <v>0.740902434724014</v>
+        <v>0.72811411692448</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -2180,21 +1944,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.00211303597616907</v>
+        <v>0.00860969021062473</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.371997294695998</v>
+        <v>1.67640534419858</v>
       </c>
       <c r="F3" t="n">
-        <v>0.710399690243109</v>
+        <v>0.0960256857041349</v>
       </c>
       <c r="G3" t="n">
-        <v>0.923519597316042</v>
+        <v>0.528141271372742</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -2203,21 +1967,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.00806444395786528</v>
+        <v>-0.000454844303956134</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.41973509650899</v>
+        <v>-0.0885633981335799</v>
       </c>
       <c r="F4" t="n">
-        <v>0.157680063651972</v>
+        <v>0.929563122605209</v>
       </c>
       <c r="G4" t="n">
-        <v>0.598927128290898</v>
+        <v>0.936759859252873</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -2226,21 +1990,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00729089081688148</v>
+        <v>-0.000408267159042391</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2835520504109</v>
+        <v>-0.0794942942819043</v>
       </c>
       <c r="F5" t="n">
-        <v>0.201202075366323</v>
+        <v>0.936759859252873</v>
       </c>
       <c r="G5" t="n">
-        <v>0.598927128290898</v>
+        <v>0.936759859252873</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -2249,21 +2013,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0064992498594498</v>
+        <v>-0.0062198626666195</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1441846672445</v>
+        <v>-1.21107853586123</v>
       </c>
       <c r="F6" t="n">
-        <v>0.254299649286859</v>
+        <v>0.228029110002537</v>
       </c>
       <c r="G6" t="n">
-        <v>0.598927128290898</v>
+        <v>0.678951741883738</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -2272,21 +2036,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.00372498458048146</v>
+        <v>-0.00446973025500284</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.655778795226975</v>
+        <v>-0.870307700196465</v>
       </c>
       <c r="F7" t="n">
-        <v>0.512932454808933</v>
+        <v>0.38571221001653</v>
       </c>
       <c r="G7" t="n">
-        <v>0.740902434724014</v>
+        <v>0.707139051696972</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -2295,21 +2059,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00392465082497711</v>
+        <v>0.00301100463086838</v>
       </c>
       <c r="E8" t="n">
-        <v>0.690929783488496</v>
+        <v>0.586277105344089</v>
       </c>
       <c r="F8" t="n">
-        <v>0.49063649098738</v>
+        <v>0.558690519948608</v>
       </c>
       <c r="G8" t="n">
-        <v>0.740902434724014</v>
+        <v>0.768199464929336</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -2318,21 +2082,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.000977670717556872</v>
+        <v>0.00592729478418539</v>
       </c>
       <c r="E9" t="n">
-        <v>0.172117685707378</v>
+        <v>1.15411221655648</v>
       </c>
       <c r="F9" t="n">
-        <v>0.863568093230675</v>
+        <v>0.250539427626391</v>
       </c>
       <c r="G9" t="n">
-        <v>0.970105140270808</v>
+        <v>0.678951741883738</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -2341,21 +2105,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.000574259631199062</v>
+        <v>0.00524918280559859</v>
       </c>
       <c r="E10" t="n">
-        <v>0.101097677308112</v>
+        <v>1.02207604370265</v>
       </c>
       <c r="F10" t="n">
-        <v>0.919602741419463</v>
+        <v>0.308614428128972</v>
       </c>
       <c r="G10" t="n">
-        <v>0.970105140270808</v>
+        <v>0.678951741883738</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -2364,21 +2128,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0127076864073645</v>
+        <v>0.00047202915423823</v>
       </c>
       <c r="E11" t="n">
-        <v>2.23717202106287</v>
+        <v>0.0919094854081962</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0266922681599369</v>
+        <v>0.926909292495257</v>
       </c>
       <c r="G11" t="n">
-        <v>0.34699948607918</v>
+        <v>0.936759859252873</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -2387,62 +2151,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.00748100748932546</v>
+        <v>-0.0095303874040708</v>
       </c>
       <c r="E12" t="n">
-        <v>1.31702184866487</v>
+        <v>-1.85567563821879</v>
       </c>
       <c r="F12" t="n">
-        <v>0.18976262837397</v>
+        <v>0.0657300458695074</v>
       </c>
       <c r="G12" t="n">
-        <v>0.598927128290898</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.000213217171941321</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.0375366117943259</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.970105140270808</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.970105140270808</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" t="n">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.00620397932322708</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1.09220266508407</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.27642790536503</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.598927128290898</v>
+        <v>0.528141271372742</v>
       </c>
     </row>
   </sheetData>
@@ -2481,7 +2199,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -2490,21 +2208,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0410155765659239</v>
+        <v>0.0000403664323634381</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.562297227042724</v>
+        <v>0.00061379900542977</v>
       </c>
       <c r="F2" t="n">
-        <v>0.574658590107077</v>
+        <v>0.999511114716218</v>
       </c>
       <c r="G2" t="n">
-        <v>0.764135253717935</v>
+        <v>0.999511114716218</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -2513,21 +2231,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0404570023774292</v>
+        <v>0.0352605431261916</v>
       </c>
       <c r="E3" t="n">
-        <v>0.554639533464203</v>
+        <v>0.536160493622741</v>
       </c>
       <c r="F3" t="n">
-        <v>0.579874517424879</v>
+        <v>0.592680670189373</v>
       </c>
       <c r="G3" t="n">
-        <v>0.764135253717935</v>
+        <v>0.724387485787011</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -2536,21 +2254,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0404430741788855</v>
+        <v>0.0852166439596888</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.554448586802604</v>
+        <v>1.29577691775149</v>
       </c>
       <c r="F4" t="n">
-        <v>0.58000486371369</v>
+        <v>0.197139982086048</v>
       </c>
       <c r="G4" t="n">
-        <v>0.764135253717935</v>
+        <v>0.683329117689074</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -2559,21 +2277,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0295445231624933</v>
+        <v>-0.0472362362466644</v>
       </c>
       <c r="E5" t="n">
-        <v>0.405036448088641</v>
+        <v>-0.718259036800814</v>
       </c>
       <c r="F5" t="n">
-        <v>0.685962952046382</v>
+        <v>0.473769453661301</v>
       </c>
       <c r="G5" t="n">
-        <v>0.810683488782087</v>
+        <v>0.683329117689074</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -2582,21 +2300,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0447500794666187</v>
+        <v>-0.0486298409445242</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.613494864654097</v>
+        <v>-0.739449742231681</v>
       </c>
       <c r="F6" t="n">
-        <v>0.54037401019182</v>
+        <v>0.460846071679975</v>
       </c>
       <c r="G6" t="n">
-        <v>0.764135253717935</v>
+        <v>0.683329117689074</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -2605,21 +2323,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.106761906347031</v>
+        <v>-0.0447865373201671</v>
       </c>
       <c r="E7" t="n">
-        <v>1.46363720612928</v>
+        <v>-0.68100970173081</v>
       </c>
       <c r="F7" t="n">
-        <v>0.145150587962317</v>
+        <v>0.4969666310466</v>
       </c>
       <c r="G7" t="n">
-        <v>0.764135253717935</v>
+        <v>0.683329117689074</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -2628,21 +2346,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0596654403260904</v>
+        <v>0.0225969162561812</v>
       </c>
       <c r="E8" t="n">
-        <v>0.817974887948232</v>
+        <v>0.343601450803132</v>
       </c>
       <c r="F8" t="n">
-        <v>0.414523307235042</v>
+        <v>0.731650704099693</v>
       </c>
       <c r="G8" t="n">
-        <v>0.764135253717935</v>
+        <v>0.804815774509662</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -2651,21 +2369,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0165446674374677</v>
+        <v>0.074550749274544</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.226816770635407</v>
+        <v>1.13359474889353</v>
       </c>
       <c r="F9" t="n">
-        <v>0.820840347152109</v>
+        <v>0.258861466045322</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8316087964978</v>
+        <v>0.683329117689074</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -2674,21 +2392,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0396131723902254</v>
+        <v>0.063146233062642</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.543071165989531</v>
+        <v>0.960181338333784</v>
       </c>
       <c r="F10" t="n">
-        <v>0.587796349013797</v>
+        <v>0.338584650553616</v>
       </c>
       <c r="G10" t="n">
-        <v>0.764135253717935</v>
+        <v>0.683329117689074</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -2697,21 +2415,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.102348052172056</v>
+        <v>-0.0613058648186906</v>
       </c>
       <c r="E11" t="n">
-        <v>1.40312609861943</v>
+        <v>-0.932197289914756</v>
       </c>
       <c r="F11" t="n">
-        <v>0.162413817825776</v>
+        <v>0.352805793767943</v>
       </c>
       <c r="G11" t="n">
-        <v>0.764135253717935</v>
+        <v>0.683329117689074</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -2720,62 +2438,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0155344799110753</v>
+        <v>-0.0531957453937157</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.21296774808246</v>
+        <v>-0.808877418786509</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8316087964978</v>
+        <v>0.419929394979466</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8316087964978</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.0628998394875881</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.862316424309091</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.389735385426377</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.764135253717935</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.073355333233213</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1.00565453223689</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.316019494450884</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.764135253717935</v>
+        <v>0.683329117689074</v>
       </c>
     </row>
   </sheetData>
@@ -2791,45 +2463,45 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s">
         <v>27</v>
-      </c>
-      <c r="B1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C1" t="s">
-        <v>29</v>
       </c>
       <c r="D1" t="s">
         <v>0</v>
       </c>
       <c r="E1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" t="s">
         <v>30</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>31</v>
-      </c>
-      <c r="G1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" t="s">
         <v>34</v>
-      </c>
-      <c r="B2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C2" t="s">
-        <v>36</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -2838,76 +2510,76 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00206205915241097</v>
+        <v>0.00203979642127084</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" t="s">
         <v>34</v>
       </c>
-      <c r="B3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" t="s">
-        <v>36</v>
-      </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00434924038756749</v>
+        <v>0.00446973025500284</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" t="s">
         <v>34</v>
       </c>
-      <c r="B4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" t="s">
-        <v>36</v>
-      </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00113375938244125</v>
+        <v>0.00101034422976069</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" t="s">
         <v>34</v>
       </c>
-      <c r="B5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" t="s">
-        <v>36</v>
-      </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -2916,24 +2588,24 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0000246225407425614</v>
+        <v>0.0000256561625278057</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
         <v>34</v>
       </c>
-      <c r="B6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" t="s">
-        <v>36</v>
-      </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -2942,50 +2614,50 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0000249713720573318</v>
+        <v>0.00002353149793292</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" t="s">
         <v>34</v>
       </c>
-      <c r="B7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" t="s">
-        <v>36</v>
-      </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0261500728190795</v>
+        <v>0.0230729182193341</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" t="s">
         <v>34</v>
       </c>
-      <c r="B8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" t="s">
-        <v>36</v>
-      </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -2994,7 +2666,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0410155765659239</v>
+        <v>0.0486298409445242</v>
       </c>
     </row>
   </sheetData>
